--- a/MonteCarloApp/simulaciones/resultados/MPI_metricas.xlsx
+++ b/MonteCarloApp/simulaciones/resultados/MPI_metricas.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15.04057860374451</v>
+        <v>2.682029008865356</v>
       </c>
       <c r="C2" t="n">
-        <v>153.11328125</v>
+        <v>153.578125</v>
       </c>
       <c r="D2" t="n">
-        <v>11.3</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>
